--- a/Data/EXCEL/Transfer/salemon/202208/8427-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/8427-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A84BBF9-C5BC-4A6B-BE9B-ACA5A2187B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6682E487-3873-4C66-8229-706AF97C78B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="8427-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF008000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1219,24 +1227,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q130"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.375" customWidth="1"/>
-    <col min="2" max="5" width="8.75" customWidth="1"/>
-    <col min="6" max="7" width="9.625" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="10.125" customWidth="1"/>
-    <col min="10" max="10" width="9.625" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="9.625" customWidth="1"/>
-    <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="10.125" customWidth="1"/>
-    <col min="15" max="15" width="9.625" customWidth="1"/>
-    <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="11.125" customWidth="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1"/>
+    <col min="2" max="5" width="12.75" customWidth="1"/>
+    <col min="6" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="15.875" customWidth="1"/>
+    <col min="9" max="9" width="14.625" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="15.875" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="15.875" customWidth="1"/>
+    <col min="14" max="14" width="14.625" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="16" max="16" width="15.875" customWidth="1"/>
+    <col min="17" max="17" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1263,7 +1271,7 @@
       <c r="P1" s="15"/>
       <c r="Q1" s="16"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="11" t="s">
         <v>4</v>
@@ -1302,7 +1310,7 @@
       </c>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -1345,7 +1353,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1384,7 +1392,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1">
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>44621</v>
       </c>
@@ -1437,7 +1445,7 @@
         <v>-100.1</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>44593</v>
       </c>
@@ -1490,7 +1498,7 @@
         <v>-100.1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1">
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>44562</v>
       </c>
@@ -1543,7 +1551,7 @@
         <v>-99.5</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>44531</v>
       </c>
@@ -1596,7 +1604,7 @@
         <v>-48.8</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1">
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>44501</v>
       </c>
@@ -1649,7 +1657,7 @@
         <v>-45.2</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>44470</v>
       </c>
@@ -1702,7 +1710,7 @@
         <v>-43.5</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="5" customFormat="1">
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>44440</v>
       </c>
@@ -1755,7 +1763,7 @@
         <v>-39.6</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>44409</v>
       </c>
@@ -1808,7 +1816,7 @@
         <v>-38.1</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1">
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>44378</v>
       </c>
@@ -1861,7 +1869,7 @@
         <v>-37.200000000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>44348</v>
       </c>
@@ -1914,7 +1922,7 @@
         <v>-36.4</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1">
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>44317</v>
       </c>
@@ -1967,7 +1975,7 @@
         <v>-34.5</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>44287</v>
       </c>
@@ -2020,7 +2028,7 @@
         <v>-34.4</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="5" customFormat="1">
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>44256</v>
       </c>
@@ -2073,7 +2081,7 @@
         <v>-29</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>44228</v>
       </c>
@@ -2126,7 +2134,7 @@
         <v>-29</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="5" customFormat="1">
+    <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>44197</v>
       </c>
@@ -2179,7 +2187,7 @@
         <v>-41.2</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>44166</v>
       </c>
@@ -2232,7 +2240,7 @@
         <v>-30.3</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="5" customFormat="1">
+    <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>44136</v>
       </c>
@@ -2285,7 +2293,7 @@
         <v>-24.1</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>44105</v>
       </c>
@@ -2338,7 +2346,7 @@
         <v>-20.100000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="5" customFormat="1">
+    <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>44075</v>
       </c>
@@ -2391,7 +2399,7 @@
         <v>-23.5</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>44044</v>
       </c>
@@ -2444,7 +2452,7 @@
         <v>-25.1</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="5" customFormat="1">
+    <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>44013</v>
       </c>
@@ -2497,7 +2505,7 @@
         <v>-25.5</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>43983</v>
       </c>
@@ -2550,7 +2558,7 @@
         <v>-26.2</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="5" customFormat="1">
+    <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>43952</v>
       </c>
@@ -2603,7 +2611,7 @@
         <v>-30.2</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>43922</v>
       </c>
@@ -2656,7 +2664,7 @@
         <v>-35.4</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="5" customFormat="1">
+    <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>43891</v>
       </c>
@@ -2709,7 +2717,7 @@
         <v>-42.4</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>43862</v>
       </c>
@@ -2762,7 +2770,7 @@
         <v>-48</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="5" customFormat="1">
+    <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>43831</v>
       </c>
@@ -2815,7 +2823,7 @@
         <v>-48.1</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>43800</v>
       </c>
@@ -2868,7 +2876,7 @@
         <v>-24.6</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="5" customFormat="1">
+    <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>43770</v>
       </c>
@@ -2921,7 +2929,7 @@
         <v>-21.6</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>43739</v>
       </c>
@@ -2974,7 +2982,7 @@
         <v>-9.89</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="5" customFormat="1">
+    <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>43709</v>
       </c>
@@ -3027,7 +3035,7 @@
         <v>-7.57</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>43678</v>
       </c>
@@ -3080,7 +3088,7 @@
         <v>-6.15</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="5" customFormat="1">
+    <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>43647</v>
       </c>
@@ -3133,7 +3141,7 @@
         <v>-5.34</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="5" customFormat="1">
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>43617</v>
       </c>
@@ -3186,7 +3194,7 @@
         <v>-3.74</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="5" customFormat="1">
+    <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>43586</v>
       </c>
@@ -3239,7 +3247,7 @@
         <v>-3.24</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="5" customFormat="1">
+    <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>43556</v>
       </c>
@@ -3292,7 +3300,7 @@
         <v>-0.85</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="5" customFormat="1">
+    <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>43525</v>
       </c>
@@ -3345,7 +3353,7 @@
         <v>-2.64</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="5" customFormat="1">
+    <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>43497</v>
       </c>
@@ -3398,7 +3406,7 @@
         <v>7.49</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="5" customFormat="1">
+    <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>43466</v>
       </c>
@@ -3451,7 +3459,7 @@
         <v>-7.47</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="5" customFormat="1">
+    <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>43435</v>
       </c>
@@ -3504,7 +3512,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="5" customFormat="1">
+    <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>43405</v>
       </c>
@@ -3557,7 +3565,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="5" customFormat="1">
+    <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>43374</v>
       </c>
@@ -3610,7 +3618,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="5" customFormat="1">
+    <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>43344</v>
       </c>
@@ -3663,7 +3671,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="5" customFormat="1">
+    <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>43313</v>
       </c>
@@ -3716,7 +3724,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="5" customFormat="1">
+    <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>43282</v>
       </c>
@@ -3769,7 +3777,7 @@
         <v>9.9499999999999993</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="5" customFormat="1">
+    <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>43252</v>
       </c>
@@ -3822,7 +3830,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="5" customFormat="1">
+    <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>43221</v>
       </c>
@@ -3875,7 +3883,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="52" spans="1:17" s="5" customFormat="1">
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>43191</v>
       </c>
@@ -3928,7 +3936,7 @@
         <v>8.51</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="5" customFormat="1">
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>43160</v>
       </c>
@@ -3981,7 +3989,7 @@
         <v>7.23</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="5" customFormat="1">
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>43132</v>
       </c>
@@ -4034,7 +4042,7 @@
         <v>-4.49</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="5" customFormat="1">
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>43101</v>
       </c>
@@ -4087,7 +4095,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="5" customFormat="1">
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>43070</v>
       </c>
@@ -4140,7 +4148,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="5" customFormat="1">
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>43040</v>
       </c>
@@ -4193,7 +4201,7 @@
         <v>3.18</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="5" customFormat="1">
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>43009</v>
       </c>
@@ -4246,7 +4254,7 @@
         <v>3.49</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="5" customFormat="1">
+    <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>42979</v>
       </c>
@@ -4299,7 +4307,7 @@
         <v>7.87</v>
       </c>
     </row>
-    <row r="60" spans="1:17" s="5" customFormat="1">
+    <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>42948</v>
       </c>
@@ -4352,7 +4360,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="5" customFormat="1">
+    <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>42917</v>
       </c>
@@ -4405,7 +4413,7 @@
         <v>8.5299999999999994</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="5" customFormat="1">
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>42887</v>
       </c>
@@ -4458,7 +4466,7 @@
         <v>6.07</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="5" customFormat="1">
+    <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>42856</v>
       </c>
@@ -4511,7 +4519,7 @@
         <v>6.14</v>
       </c>
     </row>
-    <row r="64" spans="1:17" s="5" customFormat="1">
+    <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>42826</v>
       </c>
@@ -4564,7 +4572,7 @@
         <v>6.22</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="5" customFormat="1">
+    <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>42795</v>
       </c>
@@ -4617,7 +4625,7 @@
         <v>4.38</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="5" customFormat="1">
+    <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>42767</v>
       </c>
@@ -4670,7 +4678,7 @@
         <v>8.84</v>
       </c>
     </row>
-    <row r="67" spans="1:17" s="5" customFormat="1">
+    <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>42736</v>
       </c>
@@ -4723,7 +4731,7 @@
         <v>9.65</v>
       </c>
     </row>
-    <row r="68" spans="1:17" s="5" customFormat="1">
+    <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>42705</v>
       </c>
@@ -4776,7 +4784,7 @@
         <v>-18.100000000000001</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="5" customFormat="1">
+    <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>42675</v>
       </c>
@@ -4829,7 +4837,7 @@
         <v>-18.8</v>
       </c>
     </row>
-    <row r="70" spans="1:17" s="5" customFormat="1">
+    <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>42644</v>
       </c>
@@ -4882,7 +4890,7 @@
         <v>-18.600000000000001</v>
       </c>
     </row>
-    <row r="71" spans="1:17" s="5" customFormat="1">
+    <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>42614</v>
       </c>
@@ -4935,7 +4943,7 @@
         <v>-21.5</v>
       </c>
     </row>
-    <row r="72" spans="1:17" s="5" customFormat="1">
+    <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>42583</v>
       </c>
@@ -4988,7 +4996,7 @@
         <v>-22.1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" s="5" customFormat="1">
+    <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>42552</v>
       </c>
@@ -5041,7 +5049,7 @@
         <v>-22.8</v>
       </c>
     </row>
-    <row r="74" spans="1:17" s="5" customFormat="1">
+    <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>42522</v>
       </c>
@@ -5094,7 +5102,7 @@
         <v>-22.2</v>
       </c>
     </row>
-    <row r="75" spans="1:17" s="5" customFormat="1">
+    <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>42491</v>
       </c>
@@ -5147,7 +5155,7 @@
         <v>-22</v>
       </c>
     </row>
-    <row r="76" spans="1:17" s="5" customFormat="1">
+    <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>42461</v>
       </c>
@@ -5200,7 +5208,7 @@
         <v>-22.7</v>
       </c>
     </row>
-    <row r="77" spans="1:17" s="5" customFormat="1">
+    <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>42430</v>
       </c>
@@ -5253,7 +5261,7 @@
         <v>-24.5</v>
       </c>
     </row>
-    <row r="78" spans="1:17" s="5" customFormat="1">
+    <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>42401</v>
       </c>
@@ -5306,7 +5314,7 @@
         <v>-30.9</v>
       </c>
     </row>
-    <row r="79" spans="1:17" s="5" customFormat="1">
+    <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>42370</v>
       </c>
@@ -5359,7 +5367,7 @@
         <v>-32</v>
       </c>
     </row>
-    <row r="80" spans="1:17" s="5" customFormat="1">
+    <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>42339</v>
       </c>
@@ -5412,7 +5420,7 @@
         <v>-8.49</v>
       </c>
     </row>
-    <row r="81" spans="1:17" s="5" customFormat="1">
+    <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>42309</v>
       </c>
@@ -5465,7 +5473,7 @@
         <v>-11.8</v>
       </c>
     </row>
-    <row r="82" spans="1:17" s="5" customFormat="1">
+    <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>42278</v>
       </c>
@@ -5518,7 +5526,7 @@
         <v>-8.2100000000000009</v>
       </c>
     </row>
-    <row r="83" spans="1:17" s="5" customFormat="1">
+    <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>42248</v>
       </c>
@@ -5571,7 +5579,7 @@
         <v>-11.7</v>
       </c>
     </row>
-    <row r="84" spans="1:17" s="5" customFormat="1">
+    <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>42217</v>
       </c>
@@ -5624,7 +5632,7 @@
         <v>-11.3</v>
       </c>
     </row>
-    <row r="85" spans="1:17" s="5" customFormat="1">
+    <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>42186</v>
       </c>
@@ -5677,7 +5685,7 @@
         <v>-10.199999999999999</v>
       </c>
     </row>
-    <row r="86" spans="1:17" s="5" customFormat="1">
+    <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>42156</v>
       </c>
@@ -5730,7 +5738,7 @@
         <v>-10.4</v>
       </c>
     </row>
-    <row r="87" spans="1:17" s="5" customFormat="1">
+    <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>42125</v>
       </c>
@@ -5783,7 +5791,7 @@
         <v>-10.8</v>
       </c>
     </row>
-    <row r="88" spans="1:17" s="5" customFormat="1">
+    <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
         <v>42095</v>
       </c>
@@ -5836,7 +5844,7 @@
         <v>-9.5500000000000007</v>
       </c>
     </row>
-    <row r="89" spans="1:17" s="5" customFormat="1">
+    <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>42064</v>
       </c>
@@ -5889,7 +5897,7 @@
         <v>4.53</v>
       </c>
     </row>
-    <row r="90" spans="1:17" s="5" customFormat="1">
+    <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>42036</v>
       </c>
@@ -5942,7 +5950,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="91" spans="1:17" s="5" customFormat="1">
+    <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>42005</v>
       </c>
@@ -5995,7 +6003,7 @@
         <v>38.1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" s="5" customFormat="1">
+    <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>41974</v>
       </c>
@@ -6048,7 +6056,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="93" spans="1:17" s="5" customFormat="1">
+    <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
         <v>41944</v>
       </c>
@@ -6101,7 +6109,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" s="5" customFormat="1">
+    <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>41913</v>
       </c>
@@ -6154,7 +6162,7 @@
         <v>6.04</v>
       </c>
     </row>
-    <row r="95" spans="1:17" s="5" customFormat="1">
+    <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>41883</v>
       </c>
@@ -6207,7 +6215,7 @@
         <v>5.51</v>
       </c>
     </row>
-    <row r="96" spans="1:17" s="5" customFormat="1">
+    <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>41852</v>
       </c>
@@ -6260,7 +6268,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="97" spans="1:17" s="5" customFormat="1">
+    <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>41821</v>
       </c>
@@ -6313,7 +6321,7 @@
         <v>4.88</v>
       </c>
     </row>
-    <row r="98" spans="1:17" s="5" customFormat="1">
+    <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>41791</v>
       </c>
@@ -6366,7 +6374,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="99" spans="1:17" s="5" customFormat="1">
+    <row r="99" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>41760</v>
       </c>
@@ -6419,7 +6427,7 @@
         <v>6.46</v>
       </c>
     </row>
-    <row r="100" spans="1:17" s="5" customFormat="1">
+    <row r="100" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>41730</v>
       </c>
@@ -6472,7 +6480,7 @@
         <v>4.6100000000000003</v>
       </c>
     </row>
-    <row r="101" spans="1:17" s="5" customFormat="1">
+    <row r="101" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>41699</v>
       </c>
@@ -6525,7 +6533,7 @@
         <v>-0.12</v>
       </c>
     </row>
-    <row r="102" spans="1:17" s="5" customFormat="1">
+    <row r="102" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>41671</v>
       </c>
@@ -6578,7 +6586,7 @@
         <v>-12.2</v>
       </c>
     </row>
-    <row r="103" spans="1:17" s="5" customFormat="1">
+    <row r="103" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
         <v>41640</v>
       </c>
@@ -6631,7 +6639,7 @@
         <v>-25.7</v>
       </c>
     </row>
-    <row r="104" spans="1:17" s="5" customFormat="1">
+    <row r="104" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
         <v>41609</v>
       </c>
@@ -6684,7 +6692,7 @@
         <v>-12.2</v>
       </c>
     </row>
-    <row r="105" spans="1:17" s="5" customFormat="1">
+    <row r="105" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>41579</v>
       </c>
@@ -6737,7 +6745,7 @@
         <v>-11.6</v>
       </c>
     </row>
-    <row r="106" spans="1:17" s="5" customFormat="1">
+    <row r="106" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>41548</v>
       </c>
@@ -6790,7 +6798,7 @@
         <v>-18.100000000000001</v>
       </c>
     </row>
-    <row r="107" spans="1:17" s="5" customFormat="1">
+    <row r="107" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
         <v>41518</v>
       </c>
@@ -6843,7 +6851,7 @@
         <v>-18.7</v>
       </c>
     </row>
-    <row r="108" spans="1:17" s="5" customFormat="1">
+    <row r="108" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>41487</v>
       </c>
@@ -6896,7 +6904,7 @@
         <v>-18.7</v>
       </c>
     </row>
-    <row r="109" spans="1:17" s="5" customFormat="1">
+    <row r="109" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>41456</v>
       </c>
@@ -6949,7 +6957,7 @@
         <v>-18.100000000000001</v>
       </c>
     </row>
-    <row r="110" spans="1:17" s="5" customFormat="1">
+    <row r="110" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>41426</v>
       </c>
@@ -7002,7 +7010,7 @@
         <v>-17.899999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:17" s="5" customFormat="1">
+    <row r="111" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>41395</v>
       </c>
@@ -7055,7 +7063,7 @@
         <v>-19</v>
       </c>
     </row>
-    <row r="112" spans="1:17" s="5" customFormat="1">
+    <row r="112" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
         <v>41365</v>
       </c>
@@ -7108,7 +7116,7 @@
         <v>-16</v>
       </c>
     </row>
-    <row r="113" spans="1:17" s="5" customFormat="1">
+    <row r="113" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
         <v>41334</v>
       </c>
@@ -7161,7 +7169,7 @@
         <v>-14.8</v>
       </c>
     </row>
-    <row r="114" spans="1:17" s="5" customFormat="1">
+    <row r="114" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
         <v>41306</v>
       </c>
@@ -7214,7 +7222,7 @@
         <v>-5.89</v>
       </c>
     </row>
-    <row r="115" spans="1:17" s="5" customFormat="1">
+    <row r="115" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
         <v>41275</v>
       </c>
@@ -7267,7 +7275,7 @@
         <v>3.42</v>
       </c>
     </row>
-    <row r="116" spans="1:17" s="5" customFormat="1">
+    <row r="116" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>41244</v>
       </c>
@@ -7320,7 +7328,7 @@
         <v>-8.7100000000000009</v>
       </c>
     </row>
-    <row r="117" spans="1:17" s="5" customFormat="1">
+    <row r="117" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
         <v>41214</v>
       </c>
@@ -7373,7 +7381,7 @@
         <v>-12.1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" s="5" customFormat="1">
+    <row r="118" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
         <v>41183</v>
       </c>
@@ -7426,7 +7434,7 @@
         <v>-11</v>
       </c>
     </row>
-    <row r="119" spans="1:17" s="5" customFormat="1">
+    <row r="119" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
         <v>41153</v>
       </c>
@@ -7479,7 +7487,7 @@
         <v>-11.4</v>
       </c>
     </row>
-    <row r="120" spans="1:17" s="5" customFormat="1">
+    <row r="120" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
         <v>41122</v>
       </c>
@@ -7532,7 +7540,7 @@
         <v>-12</v>
       </c>
     </row>
-    <row r="121" spans="1:17" s="5" customFormat="1">
+    <row r="121" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
         <v>41091</v>
       </c>
@@ -7585,7 +7593,7 @@
         <v>-11.5</v>
       </c>
     </row>
-    <row r="122" spans="1:17" s="5" customFormat="1">
+    <row r="122" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>41061</v>
       </c>
@@ -7638,7 +7646,7 @@
         <v>-12.9</v>
       </c>
     </row>
-    <row r="123" spans="1:17" s="5" customFormat="1">
+    <row r="123" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
         <v>41030</v>
       </c>
@@ -7691,7 +7699,7 @@
         <v>-12.1</v>
       </c>
     </row>
-    <row r="124" spans="1:17" s="5" customFormat="1">
+    <row r="124" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
         <v>41000</v>
       </c>
@@ -7744,7 +7752,7 @@
         <v>-12</v>
       </c>
     </row>
-    <row r="125" spans="1:17" s="5" customFormat="1">
+    <row r="125" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
         <v>40969</v>
       </c>
@@ -7797,7 +7805,7 @@
         <v>-11.7</v>
       </c>
     </row>
-    <row r="126" spans="1:17" s="5" customFormat="1">
+    <row r="126" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
         <v>40940</v>
       </c>
@@ -7850,7 +7858,7 @@
         <v>-8.09</v>
       </c>
     </row>
-    <row r="127" spans="1:17" s="5" customFormat="1">
+    <row r="127" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
         <v>40909</v>
       </c>
@@ -7903,7 +7911,7 @@
         <v>-12.9</v>
       </c>
     </row>
-    <row r="128" spans="1:17" s="5" customFormat="1">
+    <row r="128" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
         <v>40878</v>
       </c>
@@ -7956,7 +7964,7 @@
         <v>-4.96</v>
       </c>
     </row>
-    <row r="129" spans="1:17" s="5" customFormat="1">
+    <row r="129" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
         <v>40848</v>
       </c>
@@ -8009,7 +8017,7 @@
         <v>-2.17</v>
       </c>
     </row>
-    <row r="130" spans="1:17" s="5" customFormat="1">
+    <row r="130" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
         <v>40817</v>
       </c>
@@ -8077,7 +8085,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>